--- a/EKG_Kalite_Yönetim_Sistemi/14_Çıkış Lojistiği ve Ambalaj/02_OLG2 - Ambalaj Kalitesi ve Boş Ambalaj/EKG-LOJ-MTR-01_ambalaj_muayene_ve_karar_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/14_Çıkış Lojistiği ve Ambalaj/02_OLG2 - Ambalaj Kalitesi ve Boş Ambalaj/EKG-LOJ-MTR-01_ambalaj_muayene_ve_karar_matrisi.xlsx
@@ -931,7 +931,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Ambalaj Muayene ve Karar Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Ambalaj kabul kriterleri kaynağa bağlandı; karantina, onarım ve KPI sayım kuralları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1109,7 +1110,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Ambalaj Muayene ve Karar Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Ambalaj kabul kriterleri kaynağa bağlandı; karantina, onarım ve KPI sayım kuralları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>